--- a/raw_data/P2_1948_1969/P2_raw_metadata_final.xlsx
+++ b/raw_data/P2_1948_1969/P2_raw_metadata_final.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf938313c90dc4d1/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nameer Hussain\Desktop\new format\urdu_complexity_project\raw_data\P2_1948_1969\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ADA6B6D-1729-40C7-A609-4B55DC29288F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123CE083-3B92-476E-AB26-DE5CAEEC6666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{85C25693-3EAF-4738-8048-8A9C05C734D9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DECF2C65-4E7F-44C5-8708-C2E3480B42D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="P2_raw_metadata_final" sheetId="1" r:id="rId1"/>
+    <sheet name="P2_raw_metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="209">
   <si>
     <t>file_id</t>
   </si>
@@ -61,6 +61,15 @@
     <t>P2_1950_078</t>
   </si>
   <si>
+    <t>Hamari_Dastaanain</t>
+  </si>
+  <si>
+    <t>Humaari_Daastane</t>
+  </si>
+  <si>
+    <t>Khali_Botlain_Khali_Dabbay</t>
+  </si>
+  <si>
     <t>P2_1950_066</t>
   </si>
   <si>
@@ -82,6 +91,30 @@
     <t>P2_1969_067</t>
   </si>
   <si>
+    <t>Tareekh_e_Adab_e_Urdu_(Syed_Murtaza_Hussain_Fazal_Luckhnavi)</t>
+  </si>
+  <si>
+    <t>چند_یادیں_چند_تاثرات_مصنف_عاشق_حسین_بٹالوی_1969ء_ناشر_آئینۂ_ادب</t>
+  </si>
+  <si>
+    <t>Biography</t>
+  </si>
+  <si>
+    <t>Company_Ki_Hakumat</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Falsafa_e_Islam_Part_001</t>
+  </si>
+  <si>
+    <t>Hindustan_Ke_Ahd_e_Wusta_Ki_Ek_Jhalak</t>
+  </si>
+  <si>
+    <t>Tareekh_e_Islam_Part_01</t>
+  </si>
+  <si>
     <t>P2_1967_060</t>
   </si>
   <si>
@@ -328,15 +361,18 @@
     <t>P2_1952_054</t>
   </si>
   <si>
+    <t>Ahlebait_Aur_Islam</t>
+  </si>
+  <si>
+    <t>Religion</t>
+  </si>
+  <si>
     <t>P2_1964_072</t>
   </si>
   <si>
     <t>AL-RAHIM</t>
   </si>
   <si>
-    <t>Religion</t>
-  </si>
-  <si>
     <t>P2_1951_080</t>
   </si>
   <si>
@@ -377,6 +413,240 @@
   </si>
   <si>
     <t>P2_1962_090</t>
+  </si>
+  <si>
+    <t>Mazhab_Aur_Zindagi</t>
+  </si>
+  <si>
+    <t>Muallim_ut_Tajweed_Al_Mustafeed_New_Edition</t>
+  </si>
+  <si>
+    <t>P2_1960_149</t>
+  </si>
+  <si>
+    <t>P2_1960_150</t>
+  </si>
+  <si>
+    <t>P2_1960_151</t>
+  </si>
+  <si>
+    <t>P2_1960_152</t>
+  </si>
+  <si>
+    <t>P2_1960_153</t>
+  </si>
+  <si>
+    <t>P2_1960_154</t>
+  </si>
+  <si>
+    <t>P2_1960_155</t>
+  </si>
+  <si>
+    <t>P2_1966_147</t>
+  </si>
+  <si>
+    <t>P2_1966_148</t>
+  </si>
+  <si>
+    <t>P2_1965_103</t>
+  </si>
+  <si>
+    <t>P2_1965_104</t>
+  </si>
+  <si>
+    <t>P2_1965_105</t>
+  </si>
+  <si>
+    <t>P2_1965_106</t>
+  </si>
+  <si>
+    <t>P2_1965_107</t>
+  </si>
+  <si>
+    <t>P2_1965_108</t>
+  </si>
+  <si>
+    <t>P2_1965_109</t>
+  </si>
+  <si>
+    <t>P2_1965_110</t>
+  </si>
+  <si>
+    <t>P2_1965_111</t>
+  </si>
+  <si>
+    <t>P2_1965_112</t>
+  </si>
+  <si>
+    <t>P2_1965_113</t>
+  </si>
+  <si>
+    <t>P2_1965_114</t>
+  </si>
+  <si>
+    <t>P2_1965_115</t>
+  </si>
+  <si>
+    <t>P2_1965_116</t>
+  </si>
+  <si>
+    <t>P2_1965_117</t>
+  </si>
+  <si>
+    <t>P2_1965_118</t>
+  </si>
+  <si>
+    <t>P2_1965_119</t>
+  </si>
+  <si>
+    <t>P2_1969_091</t>
+  </si>
+  <si>
+    <t>P2_1969_092</t>
+  </si>
+  <si>
+    <t>P2_1969_093</t>
+  </si>
+  <si>
+    <t>P2_1969_094</t>
+  </si>
+  <si>
+    <t>P2_1969_095</t>
+  </si>
+  <si>
+    <t>P2_1969_096</t>
+  </si>
+  <si>
+    <t>P2_1969_097</t>
+  </si>
+  <si>
+    <t>P2_1969_098</t>
+  </si>
+  <si>
+    <t>P2_1969_099</t>
+  </si>
+  <si>
+    <t>P2_1969_100</t>
+  </si>
+  <si>
+    <t>P2_1969_101</t>
+  </si>
+  <si>
+    <t>P2_1969_102</t>
+  </si>
+  <si>
+    <t>P2_1969_161</t>
+  </si>
+  <si>
+    <t>P2_1969_162</t>
+  </si>
+  <si>
+    <t>P2_1969_163</t>
+  </si>
+  <si>
+    <t>P2_1969_164</t>
+  </si>
+  <si>
+    <t>P2_1969_165</t>
+  </si>
+  <si>
+    <t>P2_1969_166</t>
+  </si>
+  <si>
+    <t>P2_1956_140</t>
+  </si>
+  <si>
+    <t>P2_1956_141</t>
+  </si>
+  <si>
+    <t>P2_1956_142</t>
+  </si>
+  <si>
+    <t>P2_1956_143</t>
+  </si>
+  <si>
+    <t>P2_1956_144</t>
+  </si>
+  <si>
+    <t>P2_1956_145</t>
+  </si>
+  <si>
+    <t>P2_1956_146</t>
+  </si>
+  <si>
+    <t>P2_1958_127</t>
+  </si>
+  <si>
+    <t>P2_1958_128</t>
+  </si>
+  <si>
+    <t>P2_1958_129</t>
+  </si>
+  <si>
+    <t>P2_1958_130</t>
+  </si>
+  <si>
+    <t>P2_1958_131</t>
+  </si>
+  <si>
+    <t>P2_1958_132</t>
+  </si>
+  <si>
+    <t>P2_1958_133</t>
+  </si>
+  <si>
+    <t>P2_1958_134</t>
+  </si>
+  <si>
+    <t>P2_1958_135</t>
+  </si>
+  <si>
+    <t>P2_1961_137</t>
+  </si>
+  <si>
+    <t>P2_1961_138</t>
+  </si>
+  <si>
+    <t>P2_1961_139</t>
+  </si>
+  <si>
+    <t>P2_1956_120</t>
+  </si>
+  <si>
+    <t>P2_1956_121</t>
+  </si>
+  <si>
+    <t>P2_1956_122</t>
+  </si>
+  <si>
+    <t>P2_1956_123</t>
+  </si>
+  <si>
+    <t>P2_1956_124</t>
+  </si>
+  <si>
+    <t>P2_1956_125</t>
+  </si>
+  <si>
+    <t>P2_1956_126</t>
+  </si>
+  <si>
+    <t>P2_1968_156</t>
+  </si>
+  <si>
+    <t>P2_1968_157</t>
+  </si>
+  <si>
+    <t>P2_1959_158</t>
+  </si>
+  <si>
+    <t>P2_1959_159</t>
+  </si>
+  <si>
+    <t>P2_1959_160</t>
+  </si>
+  <si>
+    <t>P2_1955_136</t>
   </si>
 </sst>
 </file>
@@ -1239,14 +1509,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B9B43A-4245-42EC-BF05-FFA1C7C58FEF}">
-  <dimension ref="A1:E93"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E68468D-9A54-4E8D-8F23-8DDE4C900343}">
+  <dimension ref="A1:E169"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="8.7265625" style="1"/>
-    <col min="5" max="5" width="11.6328125" style="1" customWidth="1"/>
+    <col min="1" max="2" width="13.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="11.1796875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1370,1464 +1640,2756 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="1">
-        <v>1950</v>
+        <v>1960</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="1">
-        <v>9195</v>
+        <v>23111</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
-        <v>1951</v>
+        <v>1960</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="1">
-        <v>9919</v>
+        <v>20546</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1">
-        <v>1951</v>
+        <v>1960</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="1">
-        <v>9850</v>
+        <v>19615</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
-        <v>1951</v>
+        <v>1960</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="1">
-        <v>9900</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1">
-        <v>1969</v>
+        <v>1960</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="1">
-        <v>3971</v>
+        <v>14567</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1">
-        <v>1967</v>
+        <v>1960</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1">
-        <v>11769</v>
+        <v>13585</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1">
-        <v>1968</v>
+        <v>1960</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E14" s="1">
-        <v>12414</v>
+        <v>14644</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1">
-        <v>8702</v>
+        <v>25418</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1">
-        <v>1959</v>
+        <v>1966</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E16" s="1">
-        <v>2009</v>
+        <v>17037</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
-        <v>1959</v>
+        <v>1950</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1">
-        <v>4878</v>
+        <v>9195</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
-        <v>1964</v>
+        <v>1951</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1">
-        <v>5791</v>
+        <v>9919</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
-        <v>1961</v>
+        <v>1951</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1">
-        <v>1026</v>
+        <v>9850</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1">
-        <v>1961</v>
+        <v>1951</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E20" s="1">
-        <v>1082</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1">
-        <v>1962</v>
+        <v>1969</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E21" s="1">
-        <v>1284</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E22" s="1">
-        <v>1303</v>
+        <v>5365</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1">
-        <v>1088</v>
+        <v>7317</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E24" s="1">
-        <v>5372</v>
+        <v>15725</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1">
         <v>1965</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E25" s="1">
-        <v>1598</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1">
         <v>1965</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E26" s="1">
-        <v>1360</v>
+        <v>21240</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1">
-        <v>1944</v>
+        <v>1965</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E27" s="1">
-        <v>4211</v>
+        <v>15487</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C28" s="1">
-        <v>1945</v>
+        <v>1965</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E28" s="1">
-        <v>3827</v>
+        <v>11279</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1">
-        <v>1945</v>
+        <v>1965</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E29" s="1">
-        <v>4154</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E30" s="1">
-        <v>3067</v>
+        <v>8344</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>45</v>
+        <v>151</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C31" s="1">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E31" s="1">
-        <v>4380</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C32" s="1">
         <v>1965</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E32" s="1">
-        <v>2033</v>
+        <v>14771</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C33" s="1">
         <v>1965</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E33" s="1">
-        <v>2532</v>
+        <v>15612</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C34" s="1">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E34" s="1">
-        <v>5686</v>
+        <v>24019</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C35" s="1">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E35" s="1">
-        <v>1938</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C36" s="1">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E36" s="1">
-        <v>5338</v>
+        <v>33716</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C37" s="1">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E37" s="1">
-        <v>1647</v>
+        <v>17842</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C38" s="1">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="E38" s="1">
-        <v>1132</v>
+        <v>23886</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C39" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E39" s="1">
-        <v>4886</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C40" s="1">
-        <v>1955</v>
+        <v>1969</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E40" s="1">
-        <v>2196</v>
+        <v>7426</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1">
-        <v>1958</v>
+        <v>1969</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E41" s="1">
-        <v>1210</v>
+        <v>7094</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>57</v>
+        <v>162</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C42" s="1">
-        <v>1958</v>
+        <v>1969</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E42" s="1">
-        <v>2026</v>
+        <v>7829</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C43" s="1">
-        <v>1962</v>
+        <v>1969</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E43" s="1">
-        <v>1180</v>
+        <v>7578</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C44" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E44" s="1">
-        <v>10609</v>
+        <v>6779</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C45" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E45" s="1">
-        <v>7955</v>
+        <v>17592</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C46" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E46" s="1">
-        <v>9487</v>
+        <v>15850</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C47" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E47" s="1">
-        <v>5117</v>
+        <v>14676</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C48" s="1">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E48" s="1">
-        <v>12367</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C49" s="1">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E49" s="1">
-        <v>9907</v>
+        <v>8277</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C50" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E50" s="1">
-        <v>8935</v>
+        <v>9681</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C51" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E51" s="1">
-        <v>4312</v>
+        <v>23502</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C52" s="1">
-        <v>1960</v>
+        <v>1969</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E52" s="1">
-        <v>1038</v>
+        <v>17904</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C53" s="1">
-        <v>1960</v>
+        <v>1969</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E53" s="1">
-        <v>1513</v>
+        <v>37851</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C54" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E54" s="1">
-        <v>3816</v>
+        <v>24068</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C55" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E55" s="1">
-        <v>1018</v>
+        <v>28586</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E56" s="1">
-        <v>1275</v>
+        <v>7355</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C57" s="1">
-        <v>1970</v>
+        <v>1956</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E57" s="1">
-        <v>840</v>
+        <v>14805</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1">
-        <v>1965</v>
+        <v>1956</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E58" s="1">
-        <v>6895</v>
+        <v>21858</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C59" s="1">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E59" s="1">
-        <v>2114</v>
+        <v>17386</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C60" s="1">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E60" s="1">
-        <v>350</v>
+        <v>28784</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>81</v>
+        <v>181</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C61" s="1">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E61" s="1">
-        <v>269</v>
+        <v>16990</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C62" s="1">
         <v>1956</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E62" s="1">
-        <v>763</v>
+        <v>22359</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C63" s="1">
         <v>1956</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E63" s="1">
-        <v>713</v>
+        <v>35277</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C64" s="1">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E64" s="1">
-        <v>1097</v>
+        <v>13346</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C65" s="1">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E65" s="1">
-        <v>656</v>
+        <v>16761</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C66" s="1">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E66" s="1">
-        <v>191</v>
+        <v>15778</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C67" s="1">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E67" s="1">
-        <v>1318</v>
+        <v>13462</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C68" s="1">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E68" s="1">
-        <v>382</v>
+        <v>30412</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C69" s="1">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E69" s="1">
-        <v>782</v>
+        <v>14991</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C70" s="1">
-        <v>1965</v>
+        <v>1958</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E70" s="1">
-        <v>790</v>
+        <v>21870</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C71" s="1">
-        <v>1965</v>
+        <v>1958</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E71" s="1">
-        <v>938</v>
+        <v>17126</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="C72" s="1">
-        <v>1951</v>
+        <v>1958</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="E72" s="1">
-        <v>11746</v>
+        <v>24445</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="C73" s="1">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="E73" s="1">
-        <v>5880</v>
+        <v>11785</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>96</v>
+        <v>194</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="C74" s="1">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1">
-        <v>5599</v>
+        <v>8269</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>97</v>
+        <v>195</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="C75" s="1">
-        <v>1952</v>
+        <v>1961</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="E75" s="1">
-        <v>6519</v>
+        <v>23215</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="C76" s="1">
-        <v>1952</v>
+        <v>1967</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E76" s="1">
-        <v>7952</v>
+        <v>11769</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="C77" s="1">
-        <v>1952</v>
+        <v>1968</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E77" s="1">
-        <v>6562</v>
+        <v>12414</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="C78" s="1">
-        <v>1952</v>
+        <v>1968</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="E78" s="1">
-        <v>16564</v>
+        <v>8702</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="C79" s="1">
-        <v>1952</v>
+        <v>1959</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="E79" s="1">
-        <v>14727</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="C80" s="1">
-        <v>1964</v>
+        <v>1959</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E80" s="1">
-        <v>7538</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="C81" s="1">
-        <v>1951</v>
+        <v>1964</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E81" s="1">
-        <v>8716</v>
+        <v>5791</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C82" s="1">
-        <v>1951</v>
+        <v>1961</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E82" s="1">
-        <v>8269</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C83" s="1">
-        <v>1954</v>
+        <v>1961</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E83" s="1">
-        <v>7883</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C84" s="1">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E84" s="1">
-        <v>7970</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C85" s="1">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E85" s="1">
-        <v>2122</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C86" s="1">
-        <v>1955</v>
+        <v>1962</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E86" s="1">
-        <v>6984</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C87" s="1">
-        <v>1955</v>
+        <v>1962</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E87" s="1">
-        <v>8787</v>
+        <v>5372</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C88" s="1">
-        <v>1955</v>
+        <v>1965</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E88" s="1">
-        <v>4243</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C89" s="1">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>104</v>
+        <v>38</v>
       </c>
       <c r="E89" s="1">
-        <v>11774</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="C90" s="1">
-        <v>1961</v>
+        <v>1944</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="E90" s="1">
-        <v>2491</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="C91" s="1">
-        <v>1962</v>
+        <v>1945</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="E91" s="1">
-        <v>4588</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="C92" s="1">
-        <v>1962</v>
+        <v>1945</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="E92" s="1">
-        <v>3545</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C93" s="1">
+        <v>1963</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E93" s="1">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94" s="1">
+        <v>1963</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E94" s="1">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C95" s="1">
+        <v>1965</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E95" s="1">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C96" s="1">
+        <v>1965</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E96" s="1">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E97" s="1">
+        <v>5686</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E99" s="1">
+        <v>5338</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E100" s="1">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C101" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E101" s="1">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4886</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1955</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1958</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E104" s="1">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C105" s="1">
+        <v>1958</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E105" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C106" s="1">
+        <v>1962</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E106" s="1">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E107" s="1">
+        <v>10609</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E108" s="1">
+        <v>7955</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E109" s="1">
+        <v>9487</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E110" s="1">
+        <v>5117</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C111" s="1">
+        <v>1967</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E111" s="1">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C112" s="1">
+        <v>1967</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E112" s="1">
+        <v>9907</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C113" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E113" s="1">
+        <v>8935</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E114" s="1">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C115" s="1">
+        <v>1960</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E115" s="1">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C116" s="1">
+        <v>1960</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E116" s="1">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C117" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E117" s="1">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C118" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E118" s="1">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C119" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E119" s="1">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C120" s="1">
+        <v>1970</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E120" s="1">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1965</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E121" s="1">
+        <v>6895</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C122" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E122" s="1">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C123" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E123" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C124" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E124" s="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C125" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E125" s="1">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C126" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E126" s="1">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C127" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C128" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E128" s="1">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C129" s="1">
+        <v>1960</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E129" s="1">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C130" s="1">
+        <v>1960</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E130" s="1">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C131" s="1">
+        <v>1962</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E131" s="1">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C132" s="1">
+        <v>1962</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E132" s="1">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C133" s="1">
+        <v>1965</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E133" s="1">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C134" s="1">
+        <v>1965</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E134" s="1">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C135" s="1">
+        <v>1951</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E135" s="1">
+        <v>11746</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C136" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E136" s="1">
+        <v>5880</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C137" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E137" s="1">
+        <v>5599</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C138" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E138" s="1">
+        <v>6519</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C139" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E139" s="1">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C140" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E140" s="1">
+        <v>6562</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E141" s="1">
+        <v>16564</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C142" s="1">
+        <v>1952</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E142" s="1">
+        <v>14727</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1955</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E143" s="1">
+        <v>18631</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1964</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E144" s="1">
+        <v>7538</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C93" s="1">
+      <c r="C145" s="1">
+        <v>1951</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E145" s="1">
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C146" s="1">
+        <v>1951</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E146" s="1">
+        <v>8269</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C147" s="1">
+        <v>1954</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E147" s="1">
+        <v>7883</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1954</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E148" s="1">
+        <v>7970</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1954</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E149" s="1">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C150" s="1">
+        <v>1955</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E150" s="1">
+        <v>6984</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C151" s="1">
+        <v>1955</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E151" s="1">
+        <v>8787</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C152" s="1">
+        <v>1955</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E152" s="1">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1961</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E153" s="1">
+        <v>11774</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C154" s="1">
+        <v>1961</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E154" s="1">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C155" s="1">
         <v>1962</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E93" s="1">
+      <c r="D155" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E155" s="1">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C156" s="1">
+        <v>1962</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E156" s="1">
+        <v>3545</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A157" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C157" s="1">
+        <v>1962</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E157" s="1">
         <v>2462</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C158" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E158" s="1">
+        <v>14805</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A159" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C159" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E159" s="1">
+        <v>21855</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A160" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C160" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E160" s="1">
+        <v>17386</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A161" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C161" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E161" s="1">
+        <v>28806</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A162" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E162" s="1">
+        <v>15255</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A163" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E163" s="1">
+        <v>24468</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C164" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E164" s="1">
+        <v>35317</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E165" s="1">
+        <v>13667</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A166" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C166" s="1">
+        <v>1968</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E166" s="1">
+        <v>15153</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A167" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C167" s="1">
+        <v>1959</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E167" s="1">
+        <v>26913</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A168" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C168" s="1">
+        <v>1959</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E168" s="1">
+        <v>21899</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C169" s="1">
+        <v>1959</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E169" s="1">
+        <v>26198</v>
       </c>
     </row>
   </sheetData>
